--- a/templates/route_template.xlsx
+++ b/templates/route_template.xlsx
@@ -1,106 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4049B7F6-5539-4D01-8CA7-D7D3A2EDC5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Маршрутная карта" sheetId="1" r:id="rId1"/>
+    <sheet name="Маршрутная карта" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>Маршрутно-операционный лист</t>
-  </si>
-  <si>
-    <t>Изделие:</t>
-  </si>
-  <si>
-    <t>Деталь (шифр, наименование):</t>
-  </si>
-  <si>
-    <t>Дата запуска:</t>
-  </si>
-  <si>
-    <t>Количество деталей:</t>
-  </si>
-  <si>
-    <t>Материал:</t>
-  </si>
-  <si>
-    <t>Размер заготовки:</t>
-  </si>
-  <si>
-    <t>Наименование операции</t>
-  </si>
-  <si>
-    <t>Норма времени, ч</t>
-  </si>
-  <si>
-    <t>Оборудование</t>
-  </si>
-  <si>
-    <t>Исполнитель</t>
-  </si>
-  <si>
-    <t>Статус</t>
-  </si>
-  <si>
-    <t>Годных/Брак</t>
-  </si>
-  <si>
-    <t>Примечание</t>
-  </si>
-  <si>
-    <t>Документ сформировал: Орлов Александр Михайлович</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кол-во заготовок: </t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <i/>
+      <name val="Calibri"/>
+      <i val="1"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -157,84 +94,104 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>716280</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="952500" cy="952500"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6461760" y="38100"/>
-          <a:ext cx="952500" cy="952500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -521,156 +478,169 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.88671875" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
+    <col width="30.88671875" customWidth="1" style="4" min="1" max="1"/>
+    <col width="17.33203125" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="14.21875" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
+    <col width="12.44140625" customWidth="1" style="4" min="4" max="4"/>
+    <col width="8.88671875" customWidth="1" style="4" min="5" max="5"/>
+    <col width="12.6640625" bestFit="1" customWidth="1" style="4" min="6" max="6"/>
+    <col width="12.109375" bestFit="1" customWidth="1" style="4" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Маршрутно-операционный лист</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Изделие:</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Деталь (шифр, наименование):</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Дата запуска:</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Количество деталей:</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Материал:</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Размер заготовки:</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кол-во заготовок: </t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Наименование операции</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Норма времени, ч</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Оборудование</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Исполнитель</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A12:G12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/templates/route_template.xlsx
+++ b/templates/route_template.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,11 @@
       <i val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -96,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -118,6 +123,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -483,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.88671875" customWidth="1" style="4" min="1" max="1"/>
@@ -634,7 +643,10 @@
       <c r="G10" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr"/>
+      <c r="A12" s="11" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
